--- a/activity/M03A06/M03A06_Mapificacion.xlsx
+++ b/activity/M03A06/M03A06_Mapificacion.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28403"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/william_aguilar_escuelaing_edu_co/Documents/UECIJG.Student/HCMC2024.2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="566" documentId="13_ncr:1_{D9BDCB3C-2E70-4A22-8B8F-AC3735901627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1126FB0B-A117-4FBD-A0BF-706035EA6A66}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639935D3-9855-4D1E-9917-A8CEB298EDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="16395" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Detalle!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
   <si>
     <t>Observaciones</t>
   </si>
@@ -50,31 +50,7 @@
     <t>Código</t>
   </si>
   <si>
-    <t>Promedio</t>
-  </si>
-  <si>
     <t>Requerimiento</t>
-  </si>
-  <si>
-    <t>Luego de realizada la mapificación en RAS Mapper, comprimir el modelo hidráulico como HECRAS_v1.zip.</t>
-  </si>
-  <si>
-    <t>3.6. Mapificación de resultados en Esri ArcGIS y en RAS Mapper</t>
-  </si>
-  <si>
-    <t>https://pruebacorreoescuelaingeduco.sharepoint.com/sites/HCMC/SitePages/HCMC0026.aspx</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Opcional: exportar en archivos independientes a datos GIS, los resultados de flujo permanente y no permanente para 2.33, 25 y 100 años de periodo de retorno. Incluir los mapas Water Surfaces, Water Surfaces Extents, Velocity, Shear Stress, Stream Power y en propiedades adicionales seleccione las casillas Bank Stations y Leeves. Para flujo no permanente, elegir el instante de tiempo en el que se produjo la máxima elevación de la lámina de agua. Comprimir los 6 archivos de exportación y guardar como HECRAS.RASexport.zip.</t>
-  </si>
-  <si>
-    <t>Opcional: para cada periodo de retorno, importar en ArcGIS los resultados y realizar la mapificación de cada variable; analizar los resultados obtenidos indicando en que zonas se cumple o no con las condiciones de diseño establecidas. Luego de realizada la mapificación, comprimir las bases de datos geográficas y los mapas de resultados como HECRASGIS.zip.</t>
-  </si>
-  <si>
-    <t>Crear un único reporte en Adobe Acrobat que muestre capturas de pantalla detalladas para todos los mapas obtenidos para los diferentes parámetros indicados, incluir análisis cuantitativo y si se cumplió o no con las condiciones de diseño y los valores admisibles definidos para el proyecto. Incluir portada, tabla de contenido, numeración de páginas, separadores de página para cada modelo y parámetro evaluado y observaciones detalladas. Nombrar como HCMC0025_HECRAS.pdf</t>
   </si>
   <si>
     <t>Cumple</t>
@@ -113,16 +89,43 @@
     <t>Autocalificación Alumno</t>
   </si>
   <si>
-    <t>La representación incorrecta del Tr 100 se debe los multiples controles en las secciones naturales de inicio y entrega.</t>
+    <t>Calificación: 3.6. Mapificación de resultados de modelación 1D en RAS Mapper</t>
   </si>
   <si>
-    <t>La representación incorrecta del Tr 100 se debe los multiples controles en las secciones naturales de inicio y entrega. Para el cálculo correcto no son necesarias mas secciones transversales de muestreo o interpolaciones entre secciones existentes.</t>
+    <t>Grupo 6</t>
   </si>
   <si>
-    <t>Modelación incorrecta, de acuerdo a las indicaciones de revisión de las entregas anteriores, el diseño civil 3D con el que se ensamblo el modelo no es correcto, para TR 2.33 la representación de inundación muestra que el modelo no esta correctamente creado.</t>
+    <t>Grupo 7</t>
   </si>
   <si>
-    <t>3.6. Mapificación de resultados en Esri ArcGIS o en RAS Mapper</t>
+    <t>Grupo 8</t>
+  </si>
+  <si>
+    <t>Grupo 9</t>
+  </si>
+  <si>
+    <t>Grupo 10</t>
+  </si>
+  <si>
+    <t>Grupo 11</t>
+  </si>
+  <si>
+    <t>Grupo 12</t>
+  </si>
+  <si>
+    <t>Grupo 13</t>
+  </si>
+  <si>
+    <t>Grupo 14</t>
+  </si>
+  <si>
+    <t>M03A06</t>
+  </si>
+  <si>
+    <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
+  </si>
+  <si>
+    <t>Luego de realizada la mapificación en RAS Mapper, comprimir el modelo hidráulico como HECRAS_v1_aaaammdd.zip.</t>
   </si>
 </sst>
 </file>
@@ -130,10 +133,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,12 +195,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Light"/>
@@ -210,8 +207,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="8"/>
-      <color theme="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -230,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -344,15 +353,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </left>
@@ -409,6 +409,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -416,9 +440,46 @@
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -428,9 +489,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -465,110 +526,124 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -614,7 +689,7 @@
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>3.6. Mapificación de resultados en Esri ArcGIS o en RAS Mapper</c:v>
+              <c:v>Calificación: 3.6. Mapificación de resultados de modelación 1D en RAS Mapper</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -686,9 +761,8 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="65000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -781,19 +855,19 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1048,6 +1122,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1055,7 +1130,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1640,15 +1714,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>63636</xdr:colOff>
+      <xdr:colOff>198300</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>901</xdr:rowOff>
+      <xdr:rowOff>181548</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>124299</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>27383</xdr:rowOff>
+      <xdr:colOff>256438</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1976,7 +2050,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B2:F22"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="10" customWidth="1"/>
@@ -1988,324 +2062,320 @@
     <col min="8" max="16384" width="11.3984375" style="10"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="F1" s="39" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="F4" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="34">
+        <v>5</v>
+      </c>
+      <c r="D5" s="19">
+        <f>Detalle!C9*C5/5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="36"/>
+      <c r="F5" s="21">
+        <f>AVERAGE(D5:E5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="34">
+        <v>5</v>
+      </c>
+      <c r="D6" s="19">
+        <f>Detalle!F9*C6/5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="21">
+        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="34">
+        <v>5</v>
+      </c>
+      <c r="D7" s="19">
+        <f>Detalle!I9*C7/5</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="36"/>
+      <c r="F7" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B8" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="34">
+        <v>5</v>
+      </c>
+      <c r="D8" s="19">
+        <f>Detalle!L9*C8/5</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B9" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="34">
+        <v>5</v>
+      </c>
+      <c r="D9" s="19">
+        <f>Detalle!O9*C9/5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="36"/>
+      <c r="F9" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="C10" s="34">
+        <v>5</v>
+      </c>
+      <c r="D10" s="19">
+        <f>Detalle!R9*C10/5</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="34">
+        <v>5</v>
+      </c>
+      <c r="D11" s="19">
+        <f>Detalle!U9*C11/5</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B12" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="34">
+        <v>5</v>
+      </c>
+      <c r="D12" s="19">
+        <f>Detalle!X9*C12/5</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="34">
+        <v>5</v>
+      </c>
+      <c r="D13" s="19">
+        <f>Detalle!AA9*C13/5</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="F13" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B14" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="34">
+        <v>5</v>
+      </c>
+      <c r="D14" s="19">
+        <f>Detalle!AD9*C14/5</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B15" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="34">
+        <v>5</v>
+      </c>
+      <c r="D15" s="19">
+        <f>Detalle!AG9*C15/5</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="F15" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="C16" s="34">
         <v>5</v>
       </c>
-      <c r="D5" s="25">
-        <f>Detalle!C11*C5/5</f>
+      <c r="D16" s="19">
+        <f>Detalle!AJ9*C16/5</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="36"/>
+      <c r="F16" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="34">
         <v>5</v>
       </c>
-      <c r="E5" s="25">
+      <c r="D17" s="19">
+        <f>Detalle!AM9*C17/5</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="36"/>
+      <c r="F17" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B18" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="35">
         <v>5</v>
       </c>
-      <c r="F5" s="31">
-        <f>AVERAGE(D5:E5)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="24">
-        <v>5</v>
-      </c>
-      <c r="D6" s="25">
-        <f>Detalle!F11*C6/5</f>
-        <v>5</v>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="31">
-        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="24">
-        <v>5</v>
-      </c>
-      <c r="D7" s="25">
-        <f>Detalle!I11*C7/5</f>
-        <v>5</v>
-      </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="31">
+      <c r="D18" s="32">
+        <f>Detalle!AP9*C18/5</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="37"/>
+      <c r="F18" s="33">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="24">
-        <v>5</v>
-      </c>
-      <c r="D8" s="25">
-        <f>Detalle!L11*C8/5</f>
-        <v>5</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="31">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B9" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="24">
-        <v>5</v>
-      </c>
-      <c r="D9" s="25">
-        <f>Detalle!O11*C9/5</f>
-        <v>4.25</v>
-      </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="31">
-        <f t="shared" si="0"/>
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="24">
-        <v>5</v>
-      </c>
-      <c r="D10" s="25">
-        <f>Detalle!R11*C10/5</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="24">
-        <v>5</v>
-      </c>
-      <c r="D11" s="25">
-        <f>Detalle!U11*C11/5</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="24">
-        <v>5</v>
-      </c>
-      <c r="D12" s="25">
-        <f>Detalle!X11*C12/5</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="24">
-        <v>5</v>
-      </c>
-      <c r="D13" s="25">
-        <f>Detalle!AA11*C13/5</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B14" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="24">
-        <v>5</v>
-      </c>
-      <c r="D14" s="25">
-        <f>Detalle!AD11*C14/5</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="24">
-        <v>5</v>
-      </c>
-      <c r="D15" s="25">
-        <f>Detalle!AG11*C15/5</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="24">
-        <v>5</v>
-      </c>
-      <c r="D16" s="25">
-        <f>Detalle!AJ11*C16/5</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="24">
-        <v>5</v>
-      </c>
-      <c r="D17" s="25">
-        <f>Detalle!AM11*C17/5</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="24">
-        <v>5</v>
-      </c>
-      <c r="D18" s="25">
-        <f>Detalle!AP11*C18/5</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28">
-        <f>AVERAGE(D5:D18)</f>
-        <v>1.7321428571428572</v>
-      </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="29"/>
-    </row>
-    <row r="20" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="38" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M03A06 en GitHub.</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B20:F21"/>
+  <mergeCells count="3">
+    <mergeCell ref="B2:F3"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B20" r:id="rId1" xr:uid="{C917888E-2351-4856-B5C1-3CE9E5636E0D}"/>
-  </hyperlinks>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17987CE-896A-4E26-83D1-1610B3259376}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR47"/>
+  <dimension ref="A1:AR45"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
@@ -2344,8 +2414,9 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A1" s="4"/>
-      <c r="B1" s="33" t="s">
-        <v>6</v>
+      <c r="B1" s="23" t="str">
+        <f>Calificacion!B2</f>
+        <v>Calificación: 3.6. Mapificación de resultados de modelación 1D en RAS Mapper</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -2378,762 +2449,666 @@
     </row>
     <row r="2" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="8"/>
-      <c r="B2" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="43" t="str">
+      <c r="B2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="24" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="43" t="str">
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="24" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="43" t="str">
+      <c r="G2" s="25"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="24" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="44"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="43" t="str">
+      <c r="J2" s="25"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="24" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="43" t="str">
+      <c r="M2" s="25"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="24" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="43" t="str">
+      <c r="P2" s="25"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="24" t="str">
         <f>Calificacion!$B10</f>
-        <v>N/A</v>
-      </c>
-      <c r="S2" s="44"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="43" t="str">
+        <v>Grupo 6</v>
+      </c>
+      <c r="S2" s="25"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="24" t="str">
         <f>Calificacion!$B11</f>
-        <v>N/A</v>
-      </c>
-      <c r="V2" s="44"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="43" t="str">
+        <v>Grupo 7</v>
+      </c>
+      <c r="V2" s="25"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="24" t="str">
         <f>Calificacion!$B12</f>
-        <v>N/A</v>
-      </c>
-      <c r="Y2" s="44"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="43" t="str">
+        <v>Grupo 8</v>
+      </c>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="24" t="str">
         <f>Calificacion!$B13</f>
-        <v>N/A</v>
-      </c>
-      <c r="AB2" s="44"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="43" t="str">
+        <v>Grupo 9</v>
+      </c>
+      <c r="AB2" s="25"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="24" t="str">
         <f>Calificacion!$B14</f>
-        <v>N/A</v>
-      </c>
-      <c r="AE2" s="44"/>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="43" t="str">
+        <v>Grupo 10</v>
+      </c>
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="24" t="str">
         <f>Calificacion!$B15</f>
-        <v>N/A</v>
-      </c>
-      <c r="AH2" s="44"/>
-      <c r="AI2" s="45"/>
-      <c r="AJ2" s="43" t="str">
+        <v>Grupo 11</v>
+      </c>
+      <c r="AH2" s="25"/>
+      <c r="AI2" s="26"/>
+      <c r="AJ2" s="24" t="str">
         <f>Calificacion!$B16</f>
-        <v>N/A</v>
-      </c>
-      <c r="AK2" s="44"/>
-      <c r="AL2" s="45"/>
-      <c r="AM2" s="43" t="str">
+        <v>Grupo 12</v>
+      </c>
+      <c r="AK2" s="25"/>
+      <c r="AL2" s="26"/>
+      <c r="AM2" s="24" t="str">
         <f>Calificacion!$B17</f>
-        <v>N/A</v>
-      </c>
-      <c r="AN2" s="44"/>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="43" t="str">
+        <v>Grupo 13</v>
+      </c>
+      <c r="AN2" s="25"/>
+      <c r="AO2" s="26"/>
+      <c r="AP2" s="24" t="str">
         <f>Calificacion!$B18</f>
-        <v>N/A</v>
-      </c>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="45"/>
+        <v>Grupo 14</v>
+      </c>
+      <c r="AQ2" s="25"/>
+      <c r="AR2" s="26"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="39"/>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="L3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="O3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="V3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="W3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="X3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="AB3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="AE3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="AH3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="AK3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="AN3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="AQ3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR3" s="16" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:44" ht="106.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="17"/>
-      <c r="AB4" s="12"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="17"/>
-      <c r="AE4" s="12"/>
-      <c r="AF4" s="18"/>
-      <c r="AG4" s="17"/>
-      <c r="AH4" s="12"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="17"/>
-      <c r="AK4" s="12"/>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="17"/>
-      <c r="AN4" s="12"/>
-      <c r="AO4" s="18"/>
-      <c r="AP4" s="17"/>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="18"/>
-    </row>
-    <row r="5" spans="1:44" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="12"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="17"/>
-      <c r="AB5" s="12"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="17"/>
-      <c r="AE5" s="12"/>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="17"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="18"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="17"/>
-      <c r="AN5" s="12"/>
-      <c r="AO5" s="18"/>
-      <c r="AP5" s="17"/>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="18"/>
-    </row>
-    <row r="6" spans="1:44" ht="79.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="17">
+        <v>4</v>
+      </c>
+      <c r="AR3" s="14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" ht="79.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="17">
-        <v>5</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="17">
-        <v>5</v>
-      </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="17">
-        <v>5</v>
-      </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="35">
-        <v>3.5</v>
-      </c>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="R6" s="17">
-        <v>0</v>
-      </c>
-      <c r="S6" s="12"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="17">
-        <v>0</v>
-      </c>
-      <c r="V6" s="12"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="12"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="12"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="12"/>
-      <c r="AF6" s="19"/>
-      <c r="AG6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="12"/>
-      <c r="AI6" s="19"/>
-      <c r="AJ6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="12"/>
-      <c r="AO6" s="19"/>
-      <c r="AP6" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="12"/>
-      <c r="AR6" s="19"/>
-    </row>
-    <row r="7" spans="1:44" ht="78.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="17">
-        <v>5</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="17">
-        <v>5</v>
-      </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="17">
-        <v>5</v>
-      </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="17">
-        <v>5</v>
-      </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="35">
-        <v>3.5</v>
-      </c>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" s="17">
-        <v>0</v>
-      </c>
-      <c r="S7" s="12"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="17">
-        <v>0</v>
-      </c>
-      <c r="V7" s="12"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="12"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="12"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="12"/>
-      <c r="AF7" s="19"/>
-      <c r="AG7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="19"/>
-      <c r="AJ7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="19"/>
-      <c r="AM7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="12"/>
-      <c r="AO7" s="19"/>
-      <c r="AP7" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="12"/>
-      <c r="AR7" s="19"/>
-    </row>
-    <row r="8" spans="1:44" ht="35.65" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="17">
-        <v>5</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="17">
-        <v>5</v>
-      </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="17">
-        <v>5</v>
-      </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="17">
-        <v>5</v>
-      </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="17">
-        <v>5</v>
-      </c>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="17">
-        <v>0</v>
-      </c>
-      <c r="S8" s="12"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="17">
-        <v>0</v>
-      </c>
-      <c r="V8" s="12"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="18"/>
-      <c r="AG8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="18"/>
-      <c r="AJ8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="18"/>
-      <c r="AM8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="12"/>
-      <c r="AO8" s="18"/>
-      <c r="AP8" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="12"/>
-      <c r="AR8" s="18"/>
-    </row>
-    <row r="9" spans="1:44" ht="108.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="17">
-        <v>5</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="17">
-        <v>5</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="17">
-        <v>5</v>
-      </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="17">
-        <v>5</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="17">
-        <v>5</v>
-      </c>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="17">
-        <v>0</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="17">
-        <v>0</v>
-      </c>
-      <c r="V9" s="12"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="12"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="12"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="12"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="12"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="12"/>
-      <c r="AR9" s="19"/>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B10" s="13"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="17"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="17"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="18"/>
-      <c r="AA10" s="17"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="18"/>
-      <c r="AD10" s="17"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="18"/>
-      <c r="AG10" s="17"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="18"/>
-      <c r="AJ10" s="17"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="18"/>
-      <c r="AM10" s="17"/>
-      <c r="AN10" s="12"/>
-      <c r="AO10" s="18"/>
-      <c r="AP10" s="17"/>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="18"/>
-    </row>
-    <row r="11" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="1"/>
-      <c r="B11" s="14" t="s">
+      <c r="C4" s="40">
+        <v>0</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="40">
+        <v>0</v>
+      </c>
+      <c r="G4" s="41"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="40">
+        <v>0</v>
+      </c>
+      <c r="J4" s="41"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="40">
+        <v>0</v>
+      </c>
+      <c r="M4" s="41"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="40">
+        <v>0</v>
+      </c>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="40">
+        <v>0</v>
+      </c>
+      <c r="S4" s="41"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="40">
+        <v>0</v>
+      </c>
+      <c r="V4" s="41"/>
+      <c r="W4" s="42"/>
+      <c r="X4" s="40">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="42"/>
+      <c r="AA4" s="40">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="40">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="41"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="40">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="41"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="40">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="41"/>
+      <c r="AL4" s="42"/>
+      <c r="AM4" s="40">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="41"/>
+      <c r="AO4" s="42"/>
+      <c r="AP4" s="40">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="42"/>
+    </row>
+    <row r="5" spans="1:44" ht="78.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="40"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="40"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="40"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="42"/>
+      <c r="AA5" s="40"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="42"/>
+      <c r="AD5" s="40"/>
+      <c r="AE5" s="41"/>
+      <c r="AF5" s="42"/>
+      <c r="AG5" s="40"/>
+      <c r="AH5" s="41"/>
+      <c r="AI5" s="42"/>
+      <c r="AJ5" s="40"/>
+      <c r="AK5" s="41"/>
+      <c r="AL5" s="42"/>
+      <c r="AM5" s="40"/>
+      <c r="AN5" s="41"/>
+      <c r="AO5" s="42"/>
+      <c r="AP5" s="40"/>
+      <c r="AQ5" s="41"/>
+      <c r="AR5" s="42"/>
+    </row>
+    <row r="6" spans="1:44" ht="35.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="40"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="41"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="41"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="41"/>
+      <c r="W6" s="42"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="41"/>
+      <c r="Z6" s="42"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="41"/>
+      <c r="AC6" s="42"/>
+      <c r="AD6" s="40"/>
+      <c r="AE6" s="41"/>
+      <c r="AF6" s="42"/>
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="42"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="41"/>
+      <c r="AL6" s="42"/>
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="41"/>
+      <c r="AO6" s="42"/>
+      <c r="AP6" s="40"/>
+      <c r="AQ6" s="41"/>
+      <c r="AR6" s="42"/>
+    </row>
+    <row r="7" spans="1:44" ht="108.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="40"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="41"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="41"/>
+      <c r="W7" s="42"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="41"/>
+      <c r="Z7" s="42"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="41"/>
+      <c r="AC7" s="42"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="41"/>
+      <c r="AF7" s="42"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="41"/>
+      <c r="AI7" s="42"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="41"/>
+      <c r="AL7" s="42"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="41"/>
+      <c r="AO7" s="42"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="41"/>
+      <c r="AR7" s="42"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="46"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="46"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="44"/>
+      <c r="V8" s="45"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="44"/>
+      <c r="Y8" s="45"/>
+      <c r="Z8" s="46"/>
+      <c r="AA8" s="44"/>
+      <c r="AB8" s="45"/>
+      <c r="AC8" s="46"/>
+      <c r="AD8" s="44"/>
+      <c r="AE8" s="45"/>
+      <c r="AF8" s="46"/>
+      <c r="AG8" s="44"/>
+      <c r="AH8" s="45"/>
+      <c r="AI8" s="46"/>
+      <c r="AJ8" s="44"/>
+      <c r="AK8" s="45"/>
+      <c r="AL8" s="46"/>
+      <c r="AM8" s="44"/>
+      <c r="AN8" s="45"/>
+      <c r="AO8" s="46"/>
+      <c r="AP8" s="44"/>
+      <c r="AQ8" s="45"/>
+      <c r="AR8" s="46"/>
+    </row>
+    <row r="9" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1"/>
+      <c r="B9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="40">
-        <f>AVERAGE(C4:C10)</f>
-        <v>5</v>
-      </c>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="40">
-        <f>AVERAGE(F4:F10)</f>
-        <v>5</v>
-      </c>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="40">
-        <f>AVERAGE(I4:I10)</f>
-        <v>5</v>
-      </c>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="40">
-        <f>AVERAGE(L4:L10)</f>
-        <v>5</v>
-      </c>
-      <c r="M11" s="41"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="40">
-        <f>AVERAGE(O4:O10)</f>
-        <v>4.25</v>
-      </c>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="40">
-        <f>AVERAGE(R4:R10)</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="41"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="40">
-        <f>AVERAGE(U4:U10)</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="41"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="40">
-        <f>AVERAGE(X4:X10)</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="41"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="40">
-        <f>AVERAGE(AA4:AA10)</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="41"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="40">
-        <f>AVERAGE(AD4:AD10)</f>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="41"/>
-      <c r="AF11" s="42"/>
-      <c r="AG11" s="40">
-        <f>AVERAGE(AG4:AG10)</f>
-        <v>0</v>
-      </c>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="42"/>
-      <c r="AJ11" s="40">
-        <f>AVERAGE(AJ4:AJ10)</f>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="41"/>
-      <c r="AL11" s="42"/>
-      <c r="AM11" s="40">
-        <f>AVERAGE(AM4:AM10)</f>
-        <v>0</v>
-      </c>
-      <c r="AN11" s="41"/>
-      <c r="AO11" s="42"/>
-      <c r="AP11" s="40">
-        <f>AVERAGE(AP4:AP10)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="41"/>
-      <c r="AR11" s="42"/>
+      <c r="C9" s="48">
+        <f>AVERAGE(C4:C8)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="48">
+        <f>AVERAGE(F4:F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="48"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="48">
+        <f>AVERAGE(I4:I8)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="48"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="48">
+        <f>AVERAGE(L4:L8)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="48"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="48">
+        <f>AVERAGE(O4:O8)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="48">
+        <f>AVERAGE(R4:R8)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="48"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="48">
+        <f>AVERAGE(U4:U8)</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="48"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="48">
+        <f>AVERAGE(X4:X8)</f>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="48">
+        <f>AVERAGE(AA4:AA8)</f>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="48">
+        <f>AVERAGE(AD4:AD8)</f>
+        <v>0</v>
+      </c>
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="49"/>
+      <c r="AG9" s="48">
+        <f>AVERAGE(AG4:AG8)</f>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="48"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="48">
+        <f>AVERAGE(AJ4:AJ8)</f>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="48"/>
+      <c r="AL9" s="49"/>
+      <c r="AM9" s="48">
+        <f>AVERAGE(AM4:AM8)</f>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="48"/>
+      <c r="AO9" s="49"/>
+      <c r="AP9" s="48">
+        <f>AVERAGE(AP4:AP8)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="48"/>
+      <c r="AR9" s="49"/>
+    </row>
+    <row r="10" spans="1:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="3"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="6"/>
+      <c r="AL10" s="6"/>
+      <c r="AM10" s="6"/>
+      <c r="AN10" s="6"/>
+      <c r="AO10" s="6"/>
+      <c r="AP10" s="6"/>
+      <c r="AQ10" s="6"/>
+      <c r="AR10" s="6"/>
+    </row>
+    <row r="11" spans="1:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="7"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="6"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="6"/>
+      <c r="AN11" s="6"/>
+      <c r="AO11" s="6"/>
+      <c r="AP11" s="6"/>
+      <c r="AQ11" s="6"/>
+      <c r="AR11" s="6"/>
     </row>
     <row r="12" spans="1:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="3"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -4662,103 +4637,26 @@
       <c r="AQ45" s="6"/>
       <c r="AR45" s="6"/>
     </row>
-    <row r="46" spans="2:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="7"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="6"/>
-      <c r="AB46" s="6"/>
-      <c r="AC46" s="6"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="6"/>
-      <c r="AO46" s="6"/>
-      <c r="AP46" s="6"/>
-      <c r="AQ46" s="6"/>
-      <c r="AR46" s="6"/>
-    </row>
-    <row r="47" spans="2:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="7"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="6"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="6"/>
-      <c r="Z47" s="6"/>
-      <c r="AA47" s="6"/>
-      <c r="AB47" s="6"/>
-      <c r="AC47" s="6"/>
-      <c r="AD47" s="6"/>
-      <c r="AE47" s="6"/>
-      <c r="AF47" s="6"/>
-      <c r="AG47" s="6"/>
-      <c r="AH47" s="6"/>
-      <c r="AI47" s="6"/>
-      <c r="AJ47" s="6"/>
-      <c r="AK47" s="6"/>
-      <c r="AL47" s="6"/>
-      <c r="AM47" s="6"/>
-      <c r="AN47" s="6"/>
-      <c r="AO47" s="6"/>
-      <c r="AP47" s="6"/>
-      <c r="AQ47" s="6"/>
-      <c r="AR47" s="6"/>
-    </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AA9:AC9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:T9"/>
     <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AP9:AR9"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="F9:H9"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="AG2:AI2"/>
@@ -4770,19 +4668,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="AM11:AO11"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="AA11:AC11"/>
-    <mergeCell ref="AD11:AF11"/>
-    <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="AJ11:AL11"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="R11:T11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M03A06/M03A06_Mapificacion.xlsx
+++ b/activity/M03A06/M03A06_Mapificacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639935D3-9855-4D1E-9917-A8CEB298EDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63ABF97-A5EE-4A69-B879-6E6399C118D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>

--- a/activity/M03A06/M03A06_Mapificacion.xlsx
+++ b/activity/M03A06/M03A06_Mapificacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63ABF97-A5EE-4A69-B879-6E6399C118D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDA99E2-30C3-4B72-93DD-CE29664E01C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -563,27 +563,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -604,9 +583,6 @@
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -640,10 +616,34 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -762,7 +762,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="65000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2063,25 +2063,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
       <c r="B4" s="15" t="s">
@@ -2104,14 +2104,14 @@
       <c r="B5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="27">
         <v>5</v>
       </c>
       <c r="D5" s="19">
         <f>Detalle!C9*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="21">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2121,14 +2121,14 @@
       <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="27">
         <v>5</v>
       </c>
       <c r="D6" s="19">
         <f>Detalle!F9*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="36"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="21">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2138,14 +2138,14 @@
       <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="27">
         <v>5</v>
       </c>
       <c r="D7" s="19">
         <f>Detalle!I9*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="36"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2155,14 +2155,14 @@
       <c r="B8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="27">
         <v>5</v>
       </c>
       <c r="D8" s="19">
         <f>Detalle!L9*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="36"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2172,14 +2172,14 @@
       <c r="B9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="27">
         <v>5</v>
       </c>
       <c r="D9" s="19">
         <f>Detalle!O9*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="36"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2189,14 +2189,14 @@
       <c r="B10" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="27">
         <v>5</v>
       </c>
       <c r="D10" s="19">
         <f>Detalle!R9*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="36"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2206,14 +2206,14 @@
       <c r="B11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="27">
         <v>5</v>
       </c>
       <c r="D11" s="19">
         <f>Detalle!U9*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="36"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2223,14 +2223,14 @@
       <c r="B12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="27">
         <v>5</v>
       </c>
       <c r="D12" s="19">
         <f>Detalle!X9*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="36"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2240,14 +2240,14 @@
       <c r="B13" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="27">
         <v>5</v>
       </c>
       <c r="D13" s="19">
         <f>Detalle!AA9*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2257,14 +2257,14 @@
       <c r="B14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="27">
         <v>5</v>
       </c>
       <c r="D14" s="19">
         <f>Detalle!AD9*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2274,14 +2274,14 @@
       <c r="B15" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="27">
         <v>5</v>
       </c>
       <c r="D15" s="19">
         <f>Detalle!AG9*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="36"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2291,14 +2291,14 @@
       <c r="B16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="27">
         <v>5</v>
       </c>
       <c r="D16" s="19">
         <f>Detalle!AJ9*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2308,52 +2308,52 @@
       <c r="B17" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="27">
         <v>5</v>
       </c>
       <c r="D17" s="19">
         <f>Detalle!AM9*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="36"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="28">
         <v>5</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="25">
         <f>Detalle!AP9*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="33">
+      <c r="E18" s="30"/>
+      <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="38" t="str">
+      <c r="B19" s="42" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A06 en GitHub.</v>
       </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="E21" s="20"/>
@@ -2449,96 +2449,96 @@
     </row>
     <row r="2" spans="1:44" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="8"/>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="24" t="str">
+      <c r="C2" s="47" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="24" t="str">
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="47" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="24" t="str">
+      <c r="G2" s="48"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="47" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="24" t="str">
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="47" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="25"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="24" t="str">
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="47" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="24" t="str">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="47" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="25"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="24" t="str">
+      <c r="S2" s="48"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="47" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="25"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="24" t="str">
+      <c r="V2" s="48"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="47" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="26"/>
-      <c r="AA2" s="24" t="str">
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="47" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="24" t="str">
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="47" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="25"/>
-      <c r="AF2" s="26"/>
-      <c r="AG2" s="24" t="str">
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="47" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="25"/>
-      <c r="AI2" s="26"/>
-      <c r="AJ2" s="24" t="str">
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="47" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="25"/>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="24" t="str">
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="47" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="25"/>
-      <c r="AO2" s="26"/>
-      <c r="AP2" s="24" t="str">
+      <c r="AN2" s="48"/>
+      <c r="AO2" s="49"/>
+      <c r="AP2" s="47" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="25"/>
-      <c r="AR2" s="26"/>
+      <c r="AQ2" s="48"/>
+      <c r="AR2" s="49"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="28"/>
+      <c r="B3" s="44"/>
       <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
@@ -2670,352 +2670,352 @@
       <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="40">
-        <v>0</v>
-      </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="40">
-        <v>0</v>
-      </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="40">
-        <v>0</v>
-      </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="40">
-        <v>0</v>
-      </c>
-      <c r="M4" s="41"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="40">
-        <v>0</v>
-      </c>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="40">
-        <v>0</v>
-      </c>
-      <c r="S4" s="41"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="40">
-        <v>0</v>
-      </c>
-      <c r="V4" s="41"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="40">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="41"/>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="41"/>
-      <c r="AL4" s="42"/>
-      <c r="AM4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="41"/>
-      <c r="AO4" s="42"/>
-      <c r="AP4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="41"/>
-      <c r="AR4" s="42"/>
+      <c r="C4" s="32">
+        <v>0</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="32">
+        <v>0</v>
+      </c>
+      <c r="G4" s="33"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="32">
+        <v>0</v>
+      </c>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="32">
+        <v>0</v>
+      </c>
+      <c r="M4" s="33"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="32">
+        <v>0</v>
+      </c>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="32">
+        <v>0</v>
+      </c>
+      <c r="S4" s="33"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="32">
+        <v>0</v>
+      </c>
+      <c r="V4" s="33"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="32">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="32">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="33"/>
+      <c r="AR4" s="34"/>
     </row>
     <row r="5" spans="1:44" ht="78.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="40"/>
-      <c r="AB5" s="41"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="41"/>
-      <c r="AF5" s="42"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="42"/>
-      <c r="AJ5" s="40"/>
-      <c r="AK5" s="41"/>
-      <c r="AL5" s="42"/>
-      <c r="AM5" s="40"/>
-      <c r="AN5" s="41"/>
-      <c r="AO5" s="42"/>
-      <c r="AP5" s="40"/>
-      <c r="AQ5" s="41"/>
-      <c r="AR5" s="42"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="32"/>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="34"/>
+      <c r="AJ5" s="32"/>
+      <c r="AK5" s="33"/>
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="32"/>
+      <c r="AN5" s="33"/>
+      <c r="AO5" s="34"/>
+      <c r="AP5" s="32"/>
+      <c r="AQ5" s="33"/>
+      <c r="AR5" s="34"/>
     </row>
     <row r="6" spans="1:44" ht="35.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="40"/>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="42"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="42"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="42"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="41"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="40"/>
-      <c r="AN6" s="41"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="40"/>
-      <c r="AQ6" s="41"/>
-      <c r="AR6" s="42"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="33"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="33"/>
+      <c r="AI6" s="34"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="33"/>
+      <c r="AL6" s="34"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="33"/>
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="33"/>
+      <c r="AR6" s="34"/>
     </row>
     <row r="7" spans="1:44" ht="108.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="41"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="42"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="41"/>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="41"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="41"/>
-      <c r="AF7" s="42"/>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="41"/>
-      <c r="AL7" s="42"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="41"/>
-      <c r="AO7" s="42"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="41"/>
-      <c r="AR7" s="42"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="33"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="33"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="32"/>
+      <c r="AN7" s="33"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="33"/>
+      <c r="AR7" s="34"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="46"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="46"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="44"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="44"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="46"/>
-      <c r="AD8" s="44"/>
-      <c r="AE8" s="45"/>
-      <c r="AF8" s="46"/>
-      <c r="AG8" s="44"/>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="46"/>
-      <c r="AJ8" s="44"/>
-      <c r="AK8" s="45"/>
-      <c r="AL8" s="46"/>
-      <c r="AM8" s="44"/>
-      <c r="AN8" s="45"/>
-      <c r="AO8" s="46"/>
-      <c r="AP8" s="44"/>
-      <c r="AQ8" s="45"/>
-      <c r="AR8" s="46"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="36"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="36"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="36"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="38"/>
+      <c r="AD8" s="36"/>
+      <c r="AE8" s="37"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="36"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="36"/>
+      <c r="AK8" s="37"/>
+      <c r="AL8" s="38"/>
+      <c r="AM8" s="36"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="38"/>
+      <c r="AP8" s="36"/>
+      <c r="AQ8" s="37"/>
+      <c r="AR8" s="38"/>
     </row>
     <row r="9" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="45">
         <f>AVERAGE(C4:C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="48">
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="45">
         <f>AVERAGE(F4:F8)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="48"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="48">
+      <c r="G9" s="45"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="45">
         <f>AVERAGE(I4:I8)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="48">
+      <c r="J9" s="45"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="45">
         <f>AVERAGE(L4:L8)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="48"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="48">
+      <c r="M9" s="45"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="45">
         <f>AVERAGE(O4:O8)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="48">
+      <c r="P9" s="45"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="45">
         <f>AVERAGE(R4:R8)</f>
         <v>0</v>
       </c>
-      <c r="S9" s="48"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="48">
+      <c r="S9" s="45"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="45">
         <f>AVERAGE(U4:U8)</f>
         <v>0</v>
       </c>
-      <c r="V9" s="48"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="48">
+      <c r="V9" s="45"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="45">
         <f>AVERAGE(X4:X8)</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="48">
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="45">
         <f>AVERAGE(AA4:AA8)</f>
         <v>0</v>
       </c>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="48">
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="46"/>
+      <c r="AD9" s="45">
         <f>AVERAGE(AD4:AD8)</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="48">
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="46"/>
+      <c r="AG9" s="45">
         <f>AVERAGE(AG4:AG8)</f>
         <v>0</v>
       </c>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="48">
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="46"/>
+      <c r="AJ9" s="45">
         <f>AVERAGE(AJ4:AJ8)</f>
         <v>0</v>
       </c>
-      <c r="AK9" s="48"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="48">
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="46"/>
+      <c r="AM9" s="45">
         <f>AVERAGE(AM4:AM8)</f>
         <v>0</v>
       </c>
-      <c r="AN9" s="48"/>
-      <c r="AO9" s="49"/>
-      <c r="AP9" s="48">
+      <c r="AN9" s="45"/>
+      <c r="AO9" s="46"/>
+      <c r="AP9" s="45">
         <f>AVERAGE(AP4:AP8)</f>
         <v>0</v>
       </c>
-      <c r="AQ9" s="48"/>
-      <c r="AR9" s="49"/>
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="46"/>
     </row>
     <row r="10" spans="1:44" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="3"/>
@@ -4639,19 +4639,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="AM9:AO9"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AA9:AC9"/>
-    <mergeCell ref="AD9:AF9"/>
-    <mergeCell ref="AG9:AI9"/>
-    <mergeCell ref="AJ9:AL9"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:T9"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP9:AR9"/>
     <mergeCell ref="C2:E2"/>
@@ -4668,6 +4655,19 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="AM9:AO9"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AA9:AC9"/>
+    <mergeCell ref="AD9:AF9"/>
+    <mergeCell ref="AG9:AI9"/>
+    <mergeCell ref="AJ9:AL9"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:T9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
